--- a/Task_4_UI_Automation_Practice/EaseBuzz_AutomationPractice/reports/test_report.xlsx
+++ b/Task_4_UI_Automation_Practice/EaseBuzz_AutomationPractice/reports/test_report.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,7 +460,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>test_dropdown_example_select_option[Option1]</t>
+          <t>test_dropdown_selection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -474,6 +474,33 @@
         </is>
       </c>
       <c r="F2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TC_XXX</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>test_radio_button_selection</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>No steps logged</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Passed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
